--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Compliant Device</t>
+    <t>EU AI System Device</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A Device profile representing an AI system, fulfilling EU AI Act metadata requirements.</t>
+    <t>A Device profile representing an AI system or software component, including system identification, versioning, intended purpose, and selected regulatory documentation metadata.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -483,8 +483,7 @@
     <t>Model Card Reference</t>
   </si>
   <si>
-    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed
- documentation, intended purpose, and risk assessments.</t>
+    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed documentation, intended purpose, and risk assessments.</t>
   </si>
   <si>
     <t>Device.modifierExtension</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4179" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4179" uniqueCount="546">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,7 +467,7 @@
     <t>Third-Country Transfer Data</t>
   </si>
   <si>
-    <t>Captures if patient data is transferred outside the EU by this device.</t>
+    <t>Documents whether use of the AI system involves a transfer of personal data to a third country or an international organisation and identifies the destination country or countries where applicable.</t>
   </si>
   <si>
     <t>Device.extension:modelCard</t>
@@ -480,10 +480,10 @@
 </t>
   </si>
   <si>
-    <t>Model Card Reference</t>
-  </si>
-  <si>
-    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed documentation, intended purpose, and risk assessments.</t>
+    <t>Reference to the AI model card</t>
+  </si>
+  <si>
+    <t>References the model card that documents the AI system's intended purpose, limitations, performance, risks, and other relevant technical information.</t>
   </si>
   <si>
     <t>Device.modifierExtension</t>
@@ -547,10 +547,10 @@
     <t>euDatabaseId</t>
   </si>
   <si>
-    <t>EU AI database registration identifier</t>
-  </si>
-  <si>
-    <t>Identifier used to document the AI system's registration entry in the EU AI database or an equivalent AI system registry.</t>
+    <t>EU AI database registration number</t>
+  </si>
+  <si>
+    <t>The unique registration number assigned to the high-risk AI system in the official EU AI database.</t>
   </si>
   <si>
     <t>Device.identifier:euDatabaseId.id</t>
@@ -647,9 +647,8 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
-    &lt;code value="eu-ai-database-id"/&gt;
-    &lt;display value="EU AI Database Identifier"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-identifier-type-cs"/&gt;
+    &lt;code value="eu-ai-registration-number"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1025,7 +1024,7 @@
     <t>Device.manufacturer</t>
   </si>
   <si>
-    <t>Name of the AI developer/manufacturer</t>
+    <t>Name of the AI manufacturer</t>
   </si>
   <si>
     <t>A name of the manufacturer or entity legally responsible for the device.</t>
@@ -1296,7 +1295,7 @@
     <t>Device.conformsTo</t>
   </si>
   <si>
-    <t>Identifies the standards, specifications, or formal guidances for the capabilities supported by the device</t>
+    <t>Applicable standards and certifications</t>
   </si>
   <si>
     <t>Identifies the standards, specifications, or formal guidances for the capabilities supported by the device. The device may be certified as conformant to these specifications e.g., communication, performance, process, measurement, or specialization standards.</t>
@@ -1329,7 +1328,7 @@
     <t>Device.conformsTo.specification</t>
   </si>
   <si>
-    <t>QMS Certification</t>
+    <t>Standard, specification, or certification</t>
   </si>
   <si>
     <t>Code that identifies the specific standard, specification, protocol, formal guidance, regulation, legislation, or certification scheme to which the device adheres.</t>
@@ -1408,6 +1407,9 @@
     <t>ceMark</t>
   </si>
   <si>
+    <t>CE marking status</t>
+  </si>
+  <si>
     <t>Device.property:ceMark.id</t>
   </si>
   <si>
@@ -1422,7 +1424,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-system-property-cs"/&gt;
     &lt;code value="ce-mark"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1437,6 +1439,9 @@
     <t>notifiedBody</t>
   </si>
   <si>
+    <t>Notified body identification number</t>
+  </si>
+  <si>
     <t>Device.property:notifiedBody.id</t>
   </si>
   <si>
@@ -1451,7 +1456,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-system-property-cs"/&gt;
     &lt;code value="notified-body-id"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1466,6 +1471,9 @@
     <t>expectedLifetime</t>
   </si>
   <si>
+    <t>Expected system lifetime</t>
+  </si>
+  <si>
     <t>Device.property:expectedLifetime.id</t>
   </si>
   <si>
@@ -1480,7 +1488,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-system-property-cs"/&gt;
     &lt;code value="expected-lifetime"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1489,43 +1497,45 @@
     <t>Device.property:expectedLifetime.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Device.property:medicalPurpose</t>
-  </si>
-  <si>
-    <t>medicalPurpose</t>
-  </si>
-  <si>
-    <t>Device.property:medicalPurpose.id</t>
-  </si>
-  <si>
-    <t>Device.property:medicalPurpose.extension</t>
-  </si>
-  <si>
-    <t>Device.property:medicalPurpose.modifierExtension</t>
-  </si>
-  <si>
-    <t>Device.property:medicalPurpose.type</t>
+    <t>Device.property:intendedPurpose</t>
+  </si>
+  <si>
+    <t>intendedPurpose</t>
+  </si>
+  <si>
+    <t>Intended purpose</t>
+  </si>
+  <si>
+    <t>Device.property:intendedPurpose.id</t>
+  </si>
+  <si>
+    <t>Device.property:intendedPurpose.extension</t>
+  </si>
+  <si>
+    <t>Device.property:intendedPurpose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Device.property:intendedPurpose.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
-    &lt;code value="medical-purpose"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-system-property-cs"/&gt;
+    &lt;code value="intended-purpose"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Device.property:medicalPurpose.value[x]</t>
+    <t>Device.property:intendedPurpose.value[x]</t>
   </si>
   <si>
     <t>Device.property:targetPopulation</t>
   </si>
   <si>
     <t>targetPopulation</t>
+  </si>
+  <si>
+    <t>Target population</t>
   </si>
   <si>
     <t>Device.property:targetPopulation.id</t>
@@ -1542,7 +1552,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-system-property-cs"/&gt;
     &lt;code value="target-population"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1599,7 +1609,7 @@
 </t>
   </si>
   <si>
-    <t>Healthcare provider responsible for the AI system</t>
+    <t>Organization responsible for the AI system</t>
   </si>
   <si>
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
@@ -1618,7 +1628,7 @@
 </t>
   </si>
   <si>
-    <t>Manufacturer Contact AND DPO Contact Details</t>
+    <t>Details for human/organization for support</t>
   </si>
   <si>
     <t>Contact details for an organization or a particular human that is responsible for the device.</t>
@@ -1703,7 +1713,7 @@
 </t>
   </si>
   <si>
-    <t>Maintenance Requirements</t>
+    <t>Device notes and comments</t>
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
@@ -4030,7 +4040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>194</v>
       </c>
@@ -4049,7 +4059,7 @@
         <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -4146,7 +4156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>206</v>
       </c>
@@ -4165,7 +4175,7 @@
         <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -4262,7 +4272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -4281,7 +4291,7 @@
         <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -7316,7 +7326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>349</v>
       </c>
@@ -7335,7 +7345,7 @@
         <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -8896,7 +8906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>402</v>
       </c>
@@ -8915,7 +8925,7 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -9021,7 +9031,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>76</v>
@@ -9574,7 +9584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>416</v>
       </c>
@@ -9593,7 +9603,7 @@
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>18</v>
@@ -10511,7 +10521,7 @@
         <v>248</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>426</v>
@@ -10596,7 +10606,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>428</v>
@@ -10708,7 +10718,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>429</v>
@@ -10822,7 +10832,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>430</v>
@@ -10938,7 +10948,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>431</v>
@@ -10982,7 +10992,7 @@
         <v>18</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>18</v>
@@ -11050,7 +11060,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>436</v>
@@ -11076,7 +11086,7 @@
         <v>18</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>438</v>
@@ -11164,13 +11174,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>423</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>18</v>
@@ -11195,7 +11205,7 @@
         <v>248</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>426</v>
@@ -11280,7 +11290,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>428</v>
@@ -11392,7 +11402,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>429</v>
@@ -11506,7 +11516,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>430</v>
@@ -11622,7 +11632,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>431</v>
@@ -11666,7 +11676,7 @@
         <v>18</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>18</v>
@@ -11734,7 +11744,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>436</v>
@@ -11760,7 +11770,7 @@
         <v>18</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>438</v>
@@ -11848,13 +11858,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>423</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>18</v>
@@ -11879,7 +11889,7 @@
         <v>248</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>426</v>
@@ -11964,7 +11974,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>428</v>
@@ -12076,7 +12086,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>429</v>
@@ -12190,7 +12200,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>430</v>
@@ -12306,7 +12316,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>431</v>
@@ -12350,7 +12360,7 @@
         <v>18</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>18</v>
@@ -12418,7 +12428,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>436</v>
@@ -12444,7 +12454,7 @@
         <v>18</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>438</v>
@@ -12532,13 +12542,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>423</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>18</v>
@@ -12563,7 +12573,7 @@
         <v>248</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>426</v>
@@ -12648,7 +12658,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>428</v>
@@ -12760,7 +12770,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>429</v>
@@ -12874,7 +12884,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>430</v>
@@ -12990,7 +13000,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>431</v>
@@ -13034,7 +13044,7 @@
         <v>18</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>18</v>
@@ -13102,7 +13112,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>436</v>
@@ -13128,7 +13138,7 @@
         <v>18</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>438</v>
@@ -13216,13 +13226,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>423</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>18</v>
@@ -13247,7 +13257,7 @@
         <v>248</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>426</v>
@@ -13332,7 +13342,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>428</v>
@@ -13444,7 +13454,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>429</v>
@@ -13558,7 +13568,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>430</v>
@@ -13674,7 +13684,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>431</v>
@@ -13718,7 +13728,7 @@
         <v>18</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>18</v>
@@ -13786,7 +13796,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>436</v>
@@ -13812,7 +13822,7 @@
         <v>18</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>196</v>
+        <v>437</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>438</v>
@@ -13900,10 +13910,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13929,10 +13939,10 @@
         <v>196</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13962,28 +13972,28 @@
         <v>375</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="Z105" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -14012,10 +14022,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14038,13 +14048,13 @@
         <v>18</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14095,7 +14105,7 @@
         <v>18</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14124,10 +14134,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14150,13 +14160,13 @@
         <v>18</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14207,7 +14217,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14236,10 +14246,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14262,13 +14272,13 @@
         <v>18</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14319,7 +14329,7 @@
         <v>18</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -14334,10 +14344,10 @@
         <v>97</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>18</v>
@@ -14346,12 +14356,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14359,13 +14369,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>18</v>
@@ -14374,16 +14384,16 @@
         <v>18</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14433,7 +14443,7 @@
         <v>18</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -14448,10 +14458,10 @@
         <v>97</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>18</v>
@@ -14462,10 +14472,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14488,17 +14498,17 @@
         <v>18</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>18</v>
@@ -14547,7 +14557,7 @@
         <v>18</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
@@ -14562,10 +14572,10 @@
         <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>18</v>
@@ -14576,10 +14586,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14605,13 +14615,13 @@
         <v>99</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14661,7 +14671,7 @@
         <v>18</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -14676,10 +14686,10 @@
         <v>97</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>18</v>
@@ -14690,10 +14700,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14716,13 +14726,13 @@
         <v>18</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14773,7 +14783,7 @@
         <v>18</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
@@ -14802,10 +14812,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14828,16 +14838,16 @@
         <v>18</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -14887,7 +14897,7 @@
         <v>18</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14914,12 +14924,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14927,13 +14937,13 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>18</v>
@@ -14942,13 +14952,13 @@
         <v>18</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14999,7 +15009,7 @@
         <v>18</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
@@ -15017,7 +15027,7 @@
         <v>18</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>18</v>
@@ -15028,10 +15038,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15057,10 +15067,10 @@
         <v>196</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15091,7 +15101,7 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>18</v>
@@ -15109,7 +15119,7 @@
         <v>18</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -15138,10 +15148,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15164,16 +15174,16 @@
         <v>18</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15223,7 +15233,7 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4179" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -427,7 +427,7 @@
     <t>Device.extension</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -484,6 +484,22 @@
   </si>
   <si>
     <t>References the model card that documents the AI system's intended purpose, limitations, performance, risks, and other relevant technical information.</t>
+  </si>
+  <si>
+    <t>Device.extension:conformityDeclaration</t>
+  </si>
+  <si>
+    <t>conformityDeclaration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-conformity-reference}
+</t>
+  </si>
+  <si>
+    <t>Reference to the EU Conformity Declaration</t>
+  </si>
+  <si>
+    <t>The EU declaration of conformity shall identify the high-risk AI system.</t>
   </si>
   <si>
     <t>Device.modifierExtension</t>
@@ -2056,12 +2072,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.76953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.5859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3354,48 +3370,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -3443,7 +3457,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -3461,7 +3475,7 @@
         <v>18</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>18</v>
@@ -3472,18 +3486,18 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>76</v>
@@ -3492,24 +3506,26 @@
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3545,17 +3561,19 @@
         <v>18</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3567,31 +3585,29 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3600,10 +3616,10 @@
         <v>85</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -3612,16 +3628,16 @@
         <v>18</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3659,19 +3675,17 @@
         <v>18</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3686,38 +3700,40 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -3726,15 +3742,17 @@
         <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>18</v>
@@ -3783,50 +3801,50 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>18</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -3838,17 +3856,15 @@
         <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3885,37 +3901,37 @@
         <v>18</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>18</v>
@@ -3926,46 +3942,44 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3989,49 +4003,49 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>18</v>
@@ -4042,10 +4056,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4053,7 +4067,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>85</v>
@@ -4062,25 +4076,25 @@
         <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4090,7 +4104,7 @@
         <v>18</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>18</v>
@@ -4105,13 +4119,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -4129,7 +4143,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -4147,7 +4161,7 @@
         <v>18</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>18</v>
@@ -4158,10 +4172,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4184,19 +4198,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
@@ -4206,10 +4220,10 @@
         <v>18</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>18</v>
@@ -4221,13 +4235,13 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -4245,7 +4259,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -4263,7 +4277,7 @@
         <v>18</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>18</v>
@@ -4274,10 +4288,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4300,18 +4314,20 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
@@ -4323,7 +4339,7 @@
         <v>18</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>18</v>
@@ -4359,7 +4375,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -4368,7 +4384,7 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
@@ -4377,7 +4393,7 @@
         <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>18</v>
@@ -4388,10 +4404,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4399,7 +4415,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>85</v>
@@ -4414,15 +4430,17 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4435,7 +4453,7 @@
         <v>18</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>18</v>
@@ -4471,7 +4489,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -4480,7 +4498,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>97</v>
@@ -4489,7 +4507,7 @@
         <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>18</v>
@@ -4500,10 +4518,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4526,17 +4544,15 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>237</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4585,7 +4601,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4603,7 +4619,7 @@
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
@@ -4614,10 +4630,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4637,18 +4653,20 @@
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4697,7 +4715,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4715,7 +4733,7 @@
         <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>18</v>
@@ -4726,10 +4744,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4752,13 +4770,13 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4809,7 +4827,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4838,10 +4856,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4852,7 +4870,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>18</v>
@@ -4861,20 +4879,18 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>251</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4923,13 +4939,13 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
@@ -4938,10 +4954,10 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>18</v>
@@ -4952,10 +4968,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4966,7 +4982,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4975,18 +4991,20 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5035,25 +5053,25 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>18</v>
@@ -5064,21 +5082,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -5090,17 +5108,15 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5149,25 +5165,25 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>18</v>
@@ -5178,14 +5194,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5198,26 +5214,24 @@
         <v>18</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5265,7 +5279,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -5283,7 +5297,7 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>18</v>
@@ -5305,22 +5319,22 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>262</v>
@@ -5328,8 +5342,12 @@
       <c r="M29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5377,43 +5395,43 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>265</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>266</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5432,13 +5450,13 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5489,7 +5507,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>85</v>
@@ -5504,32 +5522,32 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>85</v>
@@ -5541,7 +5559,7 @@
         <v>18</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>99</v>
@@ -5553,9 +5571,7 @@
         <v>275</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5603,10 +5619,10 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>85</v>
@@ -5621,13 +5637,13 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5639,7 +5655,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5655,21 +5671,21 @@
         <v>18</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5735,25 +5751,25 @@
         <v>18</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>284</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5772,16 +5788,16 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5831,7 +5847,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5849,25 +5865,25 @@
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5883,10 +5899,10 @@
         <v>18</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>292</v>
@@ -5894,10 +5910,10 @@
       <c r="M34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>294</v>
       </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5921,13 +5937,13 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>295</v>
+        <v>18</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
@@ -5945,7 +5961,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5963,21 +5979,21 @@
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>18</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5994,22 +6010,24 @@
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6036,11 +6054,11 @@
         <v>109</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6057,7 +6075,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -6072,13 +6090,13 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>18</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>18</v>
@@ -6086,10 +6104,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6106,19 +6124,19 @@
         <v>18</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6145,13 +6163,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -6169,7 +6187,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -6184,13 +6202,13 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>18</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>18</v>
@@ -6205,7 +6223,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>312</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6224,17 +6242,15 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6259,13 +6275,13 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>18</v>
+        <v>315</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
@@ -6298,7 +6314,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>18</v>
@@ -6310,7 +6326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>316</v>
       </c>
@@ -6319,17 +6335,17 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>18</v>
+        <v>317</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
@@ -6338,15 +6354,17 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>217</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6410,24 +6428,24 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>319</v>
+        <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>130</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6435,13 +6453,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -6450,7 +6468,7 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>322</v>
@@ -6507,7 +6525,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6522,7 +6540,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>324</v>
@@ -6531,15 +6549,15 @@
         <v>18</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>325</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6562,7 +6580,7 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>327</v>
@@ -6619,7 +6637,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6634,7 +6652,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>329</v>
@@ -6674,7 +6692,7 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>217</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>332</v>
@@ -6746,7 +6764,7 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>334</v>
@@ -6786,7 +6804,7 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>337</v>
@@ -6794,9 +6812,7 @@
       <c r="M42" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>18</v>
@@ -6860,19 +6876,19 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>18</v>
-      </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>341</v>
       </c>
@@ -6885,13 +6901,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -6900,7 +6916,7 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>342</v>
@@ -6908,7 +6924,9 @@
       <c r="M43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
@@ -6963,28 +6981,28 @@
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>344</v>
+        <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>18</v>
+        <v>345</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>345</v>
+        <v>18</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>346</v>
       </c>
@@ -6997,13 +7015,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -7012,13 +7030,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>173</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>174</v>
+        <v>348</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7069,28 +7087,28 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>175</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>176</v>
+        <v>349</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -7098,21 +7116,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -7124,17 +7142,15 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7183,25 +7199,25 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>18</v>
@@ -7212,14 +7228,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7232,26 +7248,24 @@
         <v>18</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7299,7 +7313,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7317,7 +7331,7 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>18</v>
@@ -7328,42 +7342,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>262</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7411,25 +7429,25 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>18</v>
@@ -7440,14 +7458,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7466,13 +7484,13 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7499,13 +7517,13 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
@@ -7523,7 +7541,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>85</v>
@@ -7538,10 +7556,10 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>18</v>
@@ -7552,10 +7570,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7563,7 +7581,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>85</v>
@@ -7572,19 +7590,19 @@
         <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7611,13 +7629,13 @@
         <v>18</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>18</v>
+        <v>361</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>18</v>
@@ -7635,22 +7653,22 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>344</v>
+        <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>363</v>
@@ -7684,19 +7702,19 @@
         <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>365</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7756,16 +7774,16 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>18</v>
+        <v>349</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>18</v>
@@ -7776,10 +7794,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7802,17 +7820,15 @@
         <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N51" t="s" s="2">
         <v>371</v>
       </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7861,7 +7877,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7876,10 +7892,10 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>18</v>
@@ -7890,10 +7906,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7904,7 +7920,7 @@
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -7916,15 +7932,17 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -7949,13 +7967,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>376</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>377</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -7973,13 +7991,13 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>18</v>
@@ -7988,10 +8006,10 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>18</v>
+        <v>345</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>18</v>
@@ -8002,10 +8020,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8028,17 +8046,15 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8063,14 +8079,14 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
       </c>
@@ -8087,7 +8103,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -8114,12 +8130,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8127,13 +8143,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
@@ -8142,15 +8158,17 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8175,13 +8193,13 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>18</v>
@@ -8199,7 +8217,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8226,12 +8244,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8239,13 +8257,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -8254,13 +8272,13 @@
         <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>173</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>174</v>
+        <v>391</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8311,25 +8329,25 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>175</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>18</v>
@@ -8340,21 +8358,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>18</v>
@@ -8366,17 +8384,15 @@
         <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8425,25 +8441,25 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>18</v>
@@ -8454,14 +8470,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8474,26 +8490,24 @@
         <v>18</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8541,7 +8555,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8559,7 +8573,7 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>18</v>
@@ -8570,42 +8584,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>391</v>
+        <v>262</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8629,13 +8647,13 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>393</v>
+        <v>18</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>394</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
@@ -8653,25 +8671,25 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>18</v>
@@ -8689,7 +8707,7 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8708,7 +8726,7 @@
         <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>396</v>
@@ -8716,9 +8734,7 @@
       <c r="M59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -8743,13 +8759,13 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>18</v>
+        <v>399</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
@@ -8782,7 +8798,7 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>18</v>
@@ -8796,10 +8812,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8822,15 +8838,17 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -8879,7 +8897,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8894,7 +8912,7 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>18</v>
@@ -8908,10 +8926,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8919,7 +8937,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>85</v>
@@ -8934,13 +8952,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>217</v>
+        <v>326</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8991,10 +9009,10 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>85</v>
@@ -9006,7 +9024,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>18</v>
@@ -9018,12 +9036,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9031,13 +9049,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -9046,13 +9064,13 @@
         <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9103,13 +9121,13 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>18</v>
@@ -9130,12 +9148,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9146,10 +9164,10 @@
         <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -9158,13 +9176,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>173</v>
+        <v>411</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>174</v>
+        <v>412</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9215,25 +9233,25 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>175</v>
+        <v>410</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>18</v>
@@ -9244,21 +9262,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>18</v>
@@ -9270,17 +9288,15 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>18</v>
@@ -9329,25 +9345,25 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>18</v>
@@ -9358,14 +9374,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9378,26 +9394,24 @@
         <v>18</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>18</v>
       </c>
@@ -9445,7 +9459,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9463,7 +9477,7 @@
         <v>18</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>18</v>
@@ -9474,42 +9488,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>412</v>
+        <v>262</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
       </c>
@@ -9533,13 +9551,13 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>414</v>
+        <v>18</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>415</v>
+        <v>18</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
@@ -9557,25 +9575,25 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>411</v>
+        <v>264</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>18</v>
@@ -9584,7 +9602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>416</v>
       </c>
@@ -9597,13 +9615,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>18</v>
@@ -9612,7 +9630,7 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>417</v>
@@ -9645,13 +9663,13 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
@@ -9672,7 +9690,7 @@
         <v>416</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>85</v>
@@ -9696,12 +9714,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9709,13 +9727,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -9724,13 +9742,13 @@
         <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9757,13 +9775,13 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>18</v>
+        <v>424</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
@@ -9781,10 +9799,10 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>85</v>
@@ -9810,10 +9828,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9821,10 +9839,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>18</v>
@@ -9836,17 +9854,15 @@
         <v>18</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N69" t="s" s="2">
         <v>427</v>
       </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -9883,23 +9899,25 @@
         <v>18</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AC69" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>18</v>
@@ -9933,10 +9951,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>18</v>
@@ -9948,15 +9966,17 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>173</v>
+        <v>430</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -9993,37 +10013,35 @@
         <v>18</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>18</v>
@@ -10034,21 +10052,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>18</v>
@@ -10060,17 +10078,15 @@
         <v>18</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>18</v>
@@ -10119,25 +10135,25 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>18</v>
@@ -10148,14 +10164,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10168,26 +10184,24 @@
         <v>18</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>18</v>
       </c>
@@ -10235,7 +10249,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10253,7 +10267,7 @@
         <v>18</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>18</v>
@@ -10264,42 +10278,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
       </c>
@@ -10323,13 +10341,13 @@
         <v>18</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>18</v>
@@ -10347,25 +10365,25 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>18</v>
@@ -10402,17 +10420,15 @@
         <v>18</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -10437,13 +10453,13 @@
         <v>18</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>18</v>
@@ -10488,16 +10504,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>18</v>
       </c>
@@ -10509,7 +10523,7 @@
         <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>18</v>
@@ -10518,16 +10532,16 @@
         <v>18</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>443</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10577,13 +10591,13 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>18</v>
@@ -10604,26 +10618,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C76" s="2"/>
+      <c r="C76" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>18</v>
@@ -10632,15 +10648,17 @@
         <v>18</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>173</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -10689,25 +10707,25 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>18</v>
@@ -10718,21 +10736,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>18</v>
@@ -10744,17 +10762,15 @@
         <v>18</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -10803,25 +10819,25 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>18</v>
@@ -10832,14 +10848,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10852,26 +10868,24 @@
         <v>18</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>18</v>
       </c>
@@ -10919,7 +10933,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10937,7 +10951,7 @@
         <v>18</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>18</v>
@@ -10948,42 +10962,46 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>18</v>
       </c>
@@ -10992,7 +11010,7 @@
         <v>18</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>18</v>
@@ -11007,13 +11025,13 @@
         <v>18</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>18</v>
@@ -11031,25 +11049,25 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>18</v>
@@ -11060,7 +11078,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>436</v>
@@ -11086,17 +11104,15 @@
         <v>18</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>18</v>
@@ -11106,7 +11122,7 @@
         <v>18</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>18</v>
+        <v>453</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>18</v>
@@ -11121,13 +11137,13 @@
         <v>18</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>18</v>
@@ -11172,28 +11188,26 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -11202,16 +11216,16 @@
         <v>18</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11261,13 +11275,13 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>18</v>
@@ -11288,14 +11302,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C82" s="2"/>
+      <c r="C82" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>18</v>
       </c>
@@ -11307,7 +11323,7 @@
         <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>18</v>
@@ -11316,15 +11332,17 @@
         <v>18</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>173</v>
+        <v>457</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -11373,25 +11391,25 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>18</v>
@@ -11402,21 +11420,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>18</v>
@@ -11428,17 +11446,15 @@
         <v>18</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -11487,25 +11503,25 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>18</v>
@@ -11516,14 +11532,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11536,26 +11552,24 @@
         <v>18</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>18</v>
       </c>
@@ -11603,7 +11617,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11621,7 +11635,7 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>18</v>
@@ -11632,42 +11646,46 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
       </c>
@@ -11676,7 +11694,7 @@
         <v>18</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>457</v>
+        <v>18</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>18</v>
@@ -11691,13 +11709,13 @@
         <v>18</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>18</v>
@@ -11715,25 +11733,25 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>18</v>
@@ -11744,7 +11762,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>436</v>
@@ -11770,17 +11788,15 @@
         <v>18</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -11790,7 +11806,7 @@
         <v>18</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>18</v>
+        <v>462</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>18</v>
@@ -11805,13 +11821,13 @@
         <v>18</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>18</v>
@@ -11856,16 +11872,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>18</v>
       </c>
@@ -11877,7 +11891,7 @@
         <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -11886,16 +11900,16 @@
         <v>18</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11945,13 +11959,13 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>18</v>
@@ -11972,26 +11986,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C88" s="2"/>
+      <c r="C88" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>18</v>
@@ -12000,15 +12016,17 @@
         <v>18</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>173</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>18</v>
@@ -12057,25 +12075,25 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>18</v>
@@ -12086,21 +12104,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>18</v>
@@ -12112,17 +12130,15 @@
         <v>18</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>18</v>
@@ -12171,25 +12187,25 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>18</v>
@@ -12200,14 +12216,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12220,26 +12236,24 @@
         <v>18</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>18</v>
       </c>
@@ -12287,7 +12301,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -12305,7 +12319,7 @@
         <v>18</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>18</v>
@@ -12316,42 +12330,46 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>18</v>
       </c>
@@ -12360,7 +12378,7 @@
         <v>18</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>466</v>
+        <v>18</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>18</v>
@@ -12375,13 +12393,13 @@
         <v>18</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>18</v>
@@ -12399,25 +12417,25 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>18</v>
@@ -12428,7 +12446,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>436</v>
@@ -12454,17 +12472,15 @@
         <v>18</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -12474,7 +12490,7 @@
         <v>18</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>18</v>
+        <v>471</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>18</v>
@@ -12489,13 +12505,13 @@
         <v>18</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>18</v>
@@ -12540,16 +12556,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>18</v>
       </c>
@@ -12561,7 +12575,7 @@
         <v>85</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>18</v>
@@ -12570,16 +12584,16 @@
         <v>18</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12629,13 +12643,13 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>18</v>
@@ -12656,26 +12670,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C94" s="2"/>
+      <c r="C94" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -12684,15 +12700,17 @@
         <v>18</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>173</v>
+        <v>475</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -12741,25 +12759,25 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>18</v>
@@ -12770,21 +12788,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>18</v>
@@ -12796,17 +12814,15 @@
         <v>18</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -12855,25 +12871,25 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>18</v>
@@ -12884,14 +12900,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12904,26 +12920,24 @@
         <v>18</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>18</v>
       </c>
@@ -12971,7 +12985,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12989,7 +13003,7 @@
         <v>18</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>18</v>
@@ -13000,42 +13014,46 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>18</v>
       </c>
@@ -13044,7 +13062,7 @@
         <v>18</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>475</v>
+        <v>18</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>18</v>
@@ -13059,13 +13077,13 @@
         <v>18</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>18</v>
@@ -13083,25 +13101,25 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>18</v>
@@ -13112,7 +13130,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>436</v>
@@ -13138,17 +13156,15 @@
         <v>18</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>18</v>
@@ -13158,7 +13174,7 @@
         <v>18</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>18</v>
+        <v>480</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>18</v>
@@ -13173,13 +13189,13 @@
         <v>18</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>18</v>
@@ -13224,16 +13240,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>18</v>
       </c>
@@ -13242,10 +13256,10 @@
         <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>18</v>
@@ -13254,16 +13268,16 @@
         <v>18</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13313,13 +13327,13 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>18</v>
@@ -13340,26 +13354,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C100" s="2"/>
+      <c r="C100" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>18</v>
@@ -13368,15 +13384,17 @@
         <v>18</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>173</v>
+        <v>484</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>18</v>
@@ -13425,25 +13443,25 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>175</v>
+        <v>428</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>18</v>
@@ -13454,21 +13472,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>18</v>
@@ -13480,17 +13498,15 @@
         <v>18</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>18</v>
@@ -13539,25 +13555,25 @@
         <v>18</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>18</v>
@@ -13568,14 +13584,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13588,26 +13604,24 @@
         <v>18</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>18</v>
       </c>
@@ -13655,7 +13669,7 @@
         <v>18</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13673,7 +13687,7 @@
         <v>18</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>18</v>
@@ -13684,42 +13698,46 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>432</v>
+        <v>262</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
       </c>
@@ -13728,7 +13746,7 @@
         <v>18</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>484</v>
+        <v>18</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>18</v>
@@ -13743,13 +13761,13 @@
         <v>18</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>18</v>
@@ -13767,25 +13785,25 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>431</v>
+        <v>264</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>18</v>
@@ -13796,7 +13814,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>436</v>
@@ -13822,17 +13840,15 @@
         <v>18</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -13842,7 +13858,7 @@
         <v>18</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>18</v>
+        <v>489</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>18</v>
@@ -13857,13 +13873,13 @@
         <v>18</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>18</v>
@@ -13910,10 +13926,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13921,7 +13937,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>85</v>
@@ -13936,15 +13952,17 @@
         <v>18</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>196</v>
+        <v>442</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>18</v>
@@ -13969,13 +13987,13 @@
         <v>18</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>489</v>
+        <v>18</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>490</v>
+        <v>18</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>18</v>
@@ -13993,10 +14011,10 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>85</v>
@@ -14048,13 +14066,13 @@
         <v>18</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14081,13 +14099,13 @@
         <v>18</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>18</v>
+        <v>494</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>18</v>
@@ -14134,10 +14152,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14160,13 +14178,13 @@
         <v>18</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14217,7 +14235,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14244,12 +14262,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14257,13 +14275,13 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>18</v>
@@ -14272,13 +14290,13 @@
         <v>18</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14329,7 +14347,7 @@
         <v>18</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -14344,24 +14362,24 @@
         <v>97</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>503</v>
+        <v>18</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AM108" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14369,13 +14387,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>18</v>
@@ -14384,17 +14402,15 @@
         <v>18</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>509</v>
-      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>18</v>
@@ -14443,13 +14459,13 @@
         <v>18</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>18</v>
@@ -14458,10 +14474,10 @@
         <v>97</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>18</v>
@@ -14472,10 +14488,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14486,7 +14502,7 @@
         <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>18</v>
@@ -14498,18 +14514,18 @@
         <v>18</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>515</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>18</v>
       </c>
@@ -14557,13 +14573,13 @@
         <v>18</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>18</v>
@@ -14572,10 +14588,10 @@
         <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>18</v>
@@ -14586,10 +14602,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14612,18 +14628,18 @@
         <v>18</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>99</v>
+        <v>517</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>18</v>
       </c>
@@ -14671,7 +14687,7 @@
         <v>18</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -14686,7 +14702,7 @@
         <v>97</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>522</v>
@@ -14714,7 +14730,7 @@
         <v>75</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>18</v>
@@ -14726,15 +14742,17 @@
         <v>18</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>18</v>
@@ -14789,7 +14807,7 @@
         <v>75</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>18</v>
@@ -14798,10 +14816,10 @@
         <v>97</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>18</v>
+        <v>521</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>177</v>
+        <v>527</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>18</v>
@@ -14812,10 +14830,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14838,17 +14856,15 @@
         <v>18</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N113" t="s" s="2">
         <v>531</v>
       </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>18</v>
@@ -14897,7 +14913,7 @@
         <v>18</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14915,7 +14931,7 @@
         <v>18</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>18</v>
@@ -14960,7 +14976,9 @@
       <c r="M114" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N114" s="2"/>
+      <c r="N114" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>18</v>
@@ -15027,7 +15045,7 @@
         <v>18</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>536</v>
+        <v>18</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>18</v>
@@ -15061,16 +15079,16 @@
         <v>18</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>196</v>
+        <v>538</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15097,11 +15115,13 @@
         <v>18</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>540</v>
+        <v>18</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>18</v>
@@ -15137,7 +15157,7 @@
         <v>18</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>297</v>
+        <v>541</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>18</v>
@@ -15148,10 +15168,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15162,7 +15182,7 @@
         <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>18</v>
@@ -15171,10 +15191,10 @@
         <v>18</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>542</v>
+        <v>201</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>543</v>
@@ -15182,9 +15202,7 @@
       <c r="M116" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="N116" t="s" s="2">
-        <v>545</v>
-      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>18</v>
@@ -15209,13 +15227,11 @@
         <v>18</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>18</v>
+        <v>545</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>18</v>
@@ -15233,13 +15249,13 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>18</v>
@@ -15251,17 +15267,131 @@
         <v>18</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN116" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN116">
+  <autoFilter ref="A1:AN117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15271,7 +15401,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
